--- a/employee_surveys/011_organizational_growth_perception_survey--employee_surveys.xlsx
+++ b/employee_surveys/011_organizational_growth_perception_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Leadership and Mission</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Employee Engagement</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Team Collaboration</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Decision-Making</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Feedback and Improvement</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Growth Opportunities</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,11 +732,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>page_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Demographics</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>page_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_clear_and_effective</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very clear and effective</t>
         </is>
       </c>
     </row>
@@ -803,46 +849,573 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_clear_and_effective</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat clear and effective</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_very_clear_and_effective</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not very clear and effective</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>page_2_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>not_at_all_clear_and_effective</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Not at all clear and effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>page_3_choices</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>page_3_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>page_3_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>page_3_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>page_3_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>very_poor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Very poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>page_4_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>page_4_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>page_4_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>page_4_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>page_4_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>very_poor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Very poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>very_transparent</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Very transparent</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>somewhat_transparent</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Somewhat transparent</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>not_very_transparent</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Not very transparent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>not_at_all_transparent</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Not at all transparent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>very_poor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Very poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>very_open</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Very open</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>somewhat_open</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Somewhat open</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>not_very_open</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Not very open</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>not_at_all_open</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Not at all open</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>very_willing</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Very willing</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>somewhat_willing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Somewhat willing</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>not_very_willing</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Not very willing</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>not_at_all_willing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Not at all willing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>very_long</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Very long</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>somewhat_long</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Somewhat long</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>not_very_long</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Not very long</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>not_at_all_long</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Not at all long</t>
         </is>
       </c>
     </row>
